--- a/data.mn/public/datasets/nso-deaths-by-region-monthly.xlsx
+++ b/data.mn/public/datasets/nso-deaths-by-region-monthly.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,50 +415,87 @@
   </sheetPr>
   <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1" t="n">
-        <v>2026</v>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -649,7 +674,9 @@
       <c r="L5" t="n">
         <v>237</v>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>232</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -692,7 +719,9 @@
       <c r="L6" t="n">
         <v>230</v>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>238</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -735,7 +764,9 @@
       <c r="L7" t="n">
         <v>248</v>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -778,7 +809,9 @@
       <c r="L8" t="n">
         <v>223</v>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>228</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1171,7 +1204,9 @@
       <c r="L17" t="n">
         <v>90</v>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1214,7 +1249,9 @@
       <c r="L18" t="n">
         <v>88</v>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1257,7 +1294,9 @@
       <c r="L19" t="n">
         <v>84</v>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1300,7 +1339,9 @@
       <c r="L20" t="n">
         <v>101</v>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1693,7 +1734,9 @@
       <c r="L29" t="n">
         <v>243</v>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>238</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1736,7 +1779,9 @@
       <c r="L30" t="n">
         <v>290</v>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>286</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1779,7 +1824,9 @@
       <c r="L31" t="n">
         <v>251</v>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1822,7 +1869,9 @@
       <c r="L32" t="n">
         <v>282</v>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>308</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2215,7 +2264,9 @@
       <c r="L41" t="n">
         <v>778</v>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>664</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2258,7 +2309,9 @@
       <c r="L42" t="n">
         <v>736</v>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>645</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2301,7 +2354,9 @@
       <c r="L43" t="n">
         <v>779</v>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>718</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2344,7 +2399,9 @@
       <c r="L44" t="n">
         <v>729</v>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>843</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2737,7 +2794,9 @@
       <c r="L53" t="n">
         <v>148</v>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2780,7 +2839,9 @@
       <c r="L54" t="n">
         <v>138</v>
       </c>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>183</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2823,7 +2884,9 @@
       <c r="L55" t="n">
         <v>138</v>
       </c>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2866,7 +2929,9 @@
       <c r="L56" t="n">
         <v>158</v>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
